--- a/data/host_lith_stats.xlsx
+++ b/data/host_lith_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B835"/>
+  <dimension ref="A1:B828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>beach sand</t>
+          <t>igneous rock</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
@@ -487,17 +487,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>igneous rock</t>
+          <t>beach sand</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
@@ -553,21 +553,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>sandstone</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sandstone</t>
+          <t>low confidence)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -633,27 +633,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ijolite</t>
+          <t>igneous rock (inferred</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>alluvium</t>
+          <t>ijolite</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dune sand</t>
+          <t>alluvium</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -663,17 +663,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sövite</t>
+          <t>dune sand</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>shale</t>
+          <t>sövite</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -683,57 +683,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>skarn</t>
+          <t>shale</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>beach and dune sand</t>
+          <t>skarn</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>breccia</t>
+          <t>beach and dune sand</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>alluvial sediment</t>
+          <t>breccia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>calcite carbonatite</t>
+          <t>alluvial sediment</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>low confidence)</t>
+          <t>calcite carbonatite</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -753,11 +753,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>medium confidence)</t>
+          <t>dune and beach sand</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -773,11 +773,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dune and beach sand</t>
+          <t>peralkaline granite</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -803,17 +803,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>peralkaline granite</t>
+          <t>dolomite</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dolomite</t>
+          <t>quartzite</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -823,7 +823,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>quartzite</t>
+          <t>gneissic granite</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -833,31 +833,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>igneous rock (inferred</t>
+          <t>mudstone</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gneissic granite</t>
+          <t>foyaite</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>alkaline igneous / carbonatite (inferred</t>
+          <t>clay</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -873,37 +873,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>foyaite</t>
+          <t>siltstone</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>clay</t>
+          <t>phoscorite</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mudstone</t>
+          <t>phonolite</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>phoscorite</t>
+          <t>tuff</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -913,81 +913,81 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>siltstone</t>
+          <t>migmatite</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>phonolite</t>
+          <t>conglomerate</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tuff</t>
+          <t>alkaline syenite</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>conglomerate</t>
+          <t>quartz syenite</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>migmatite</t>
+          <t>biotite granite</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>alkaline syenite</t>
+          <t>bauxite</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>biotite granite</t>
+          <t>mica schist</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>quartz syenite</t>
+          <t>monzonite</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -1003,37 +1003,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bauxite</t>
+          <t>weathered carbonatite</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>mica schist</t>
+          <t>peralkaline syenite</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>monzonite</t>
+          <t>sandstone / igneous (unspecified)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dolomite carbonatite</t>
+          <t>sedimentary rock</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1043,7 +1043,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sedimentary rock</t>
+          <t>dolomite carbonatite</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1053,7 +1053,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>peralkaline syenite</t>
+          <t>agglomerate</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1063,37 +1063,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>agglomerate</t>
+          <t>melteigite</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>weathered carbonatite</t>
+          <t>intermediate intrusions</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sandstone / igneous (unspecified)</t>
+          <t>diorite</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>melteigite</t>
+          <t>gneiss / schist</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1113,7 +1113,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>intermediate intrusions</t>
+          <t>rauhaugite</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1123,7 +1123,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>diorite</t>
+          <t>beforsite</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1133,7 +1133,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>beforsite</t>
+          <t>monzogranite</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1143,7 +1143,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>monzogranite</t>
+          <t>alkaline granite</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1153,37 +1153,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rauhaugite</t>
+          <t>nordmarkite</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>gneiss / schist</t>
+          <t>lignite</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>alkaline granite</t>
+          <t>marble</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>trachyte</t>
+          <t>felsic igneous or sedimentary rock (inferred</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1193,7 +1193,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lignite</t>
+          <t>glimmerite</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1223,7 +1223,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>marble</t>
+          <t>trachyte</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1243,27 +1243,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>glimmerite</t>
+          <t>carbonatite(?)</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nordmarkite</t>
+          <t>quartz monzonite</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>pulaskite</t>
+          <t>jacupirangite</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1273,7 +1273,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>jacupirangite</t>
+          <t>dacite</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1283,7 +1283,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>carbonatite(?)</t>
+          <t>granite gneiss</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1303,7 +1303,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dacite</t>
+          <t>pulaskite</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1323,27 +1323,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>granite gneiss</t>
+          <t>metasediments</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>quartz monzonite</t>
+          <t>rhyolite</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>igneous-related hydrothermal rock</t>
+          <t>greisen</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1363,7 +1363,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>greisen</t>
+          <t>weathered granite</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1373,7 +1373,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>calc-silicate rock</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1383,7 +1383,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iron formation</t>
+          <t>andesite</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1393,7 +1393,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>metasediments</t>
+          <t>igneous-related hydrothermal rock</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1403,7 +1403,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>beach</t>
+          <t>iron formation</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1413,7 +1413,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rhyolite</t>
+          <t>calc-silicate rock</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1423,27 +1423,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>andesite</t>
+          <t>beach ridge</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>weathered granite</t>
+          <t>alkali granite</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>metamorphic rock</t>
+          <t>phosphatic siltstone</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1453,7 +1453,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>phosphatic siltstone</t>
+          <t>metamorphic rock</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1463,7 +1463,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ferrocarbonatite</t>
+          <t>rapakivi granite</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1473,7 +1473,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>beach ridge</t>
+          <t>and dune sand</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1483,7 +1483,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rapakivi granite</t>
+          <t>ferrocarbonatite</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -1493,27 +1493,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>and dune sand</t>
+          <t>dolomitic marble</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>alkali granite</t>
+          <t>paragneiss</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>eluvium</t>
+          <t>sediment</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -1523,7 +1523,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>paragneiss</t>
+          <t>ultrabasic rocks</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -1533,7 +1533,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>calciocarbonatite</t>
+          <t>granosyenite</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -1543,7 +1543,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ankerite carbonatite</t>
+          <t>igneous rock (felsic to intermediate)</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -1553,7 +1553,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sediment</t>
+          <t>beach sediment</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -1563,7 +1563,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bebedourite</t>
+          <t>shonkinite</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -1573,7 +1573,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>granosyenite</t>
+          <t>carbonatite breccia</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -1593,7 +1593,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dolomitic marble</t>
+          <t>calciocarbonatite</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1603,7 +1603,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>igneous rock (felsic to intermediate)</t>
+          <t>dolerite</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1613,7 +1613,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>riebeckite granite</t>
+          <t>alluvial sand</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -1623,7 +1623,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>beach sediment</t>
+          <t>bebedourite</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -1633,7 +1633,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>lujavrite</t>
+          <t>ankerite carbonatite</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1643,7 +1643,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>granitic gneiss</t>
+          <t>lujavrite</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -1663,7 +1663,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ultrabasic rocks</t>
+          <t>granitic gneiss</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -1673,7 +1673,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>alluvial sand</t>
+          <t>phyllite</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -1683,7 +1683,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>shonkinite</t>
+          <t>eluvium</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -1693,7 +1693,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>phyllite</t>
+          <t>riebeckite granite</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -1703,27 +1703,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>dolerite</t>
+          <t>aplite</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>carbonatite breccia</t>
+          <t>volcanic rock</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>unconsolidated pyroclastics</t>
+          <t>quartz sand</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -1743,7 +1743,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>metamorphosed phyllite and (or) mica schist</t>
+          <t>silicocarbonatite</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -1753,7 +1753,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>aplite</t>
+          <t>igneous-related hydrothermal rock (inferred</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -1763,7 +1763,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>silicocarbonatite</t>
+          <t>granite(?)</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -1783,7 +1783,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>quartz diorite</t>
+          <t>metamorphosed phyllite and (or) mica schist</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -1793,7 +1793,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>quartz-pebble conglomerate</t>
+          <t>slate</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -1803,7 +1803,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>fluvial sand</t>
+          <t>unconsolidated pyroclastics</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -1813,7 +1813,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>olivinite</t>
+          <t>unconsolidated weathered tuff</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -1823,7 +1823,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>granite(?)</t>
+          <t>arfvedsonite granite</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -1833,7 +1833,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>quartz sand</t>
+          <t>quartz-pebble conglomerate</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -1843,7 +1843,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>slate</t>
+          <t>olivinite</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1853,7 +1853,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>volcanic rock</t>
+          <t>fluvial sand</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1863,7 +1863,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>unconsolidated weathered tuff</t>
+          <t>quartz diorite</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1873,17 +1873,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>arfvedsonite granite</t>
+          <t>sandy clay</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>claystone</t>
+          <t>metasiltstone</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1893,7 +1893,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>minor syenite and nepheline syenite</t>
+          <t>granophyre</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1903,7 +1903,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>granitic rock</t>
+          <t>metamorphosed mafic volcanic rock</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1913,7 +1913,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>fluvial sediments</t>
+          <t>granitic rock</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1923,7 +1923,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>alaskite</t>
+          <t>phlogopite</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1933,7 +1933,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>iron oxide breccia</t>
+          <t>weathered biotite granite</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1943,7 +1943,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>serpentinite</t>
+          <t>silexite</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1953,7 +1953,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>felsic volcanic rock</t>
+          <t>sandy gravel</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1963,7 +1963,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>silexite</t>
+          <t>silica breccia</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1973,7 +1973,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>carbonatite tuff</t>
+          <t>basalt</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1983,7 +1983,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>carbonatite / alkaline igneous</t>
+          <t>felsic volcanic rock</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -2003,7 +2003,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>basalt</t>
+          <t>iron oxide rock</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -2013,7 +2013,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rhyolitic to syenitic volcanic rock</t>
+          <t>saprolite</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -2023,7 +2023,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>carbonaceous sand</t>
+          <t>volcanics</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2033,7 +2033,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>black sand</t>
+          <t>coastal sediments</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -2043,7 +2043,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>weathered biotite granite</t>
+          <t>sandstone(?)</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -2053,7 +2053,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>nephelinite</t>
+          <t>minor syenite and nepheline syenite</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2063,7 +2063,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>metasiltstone</t>
+          <t>quartz pebble conglomerate</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -2073,7 +2073,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sandy clay</t>
+          <t>rhyolitic to syenitic volcanic rock</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2083,7 +2083,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>coastal sediments</t>
+          <t>eluvial and alluvial sediments</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2093,7 +2093,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>banded carbonates</t>
+          <t>iron oxide breccia</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -2103,7 +2103,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sandy gravel</t>
+          <t>serpentinite</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2113,7 +2113,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>granophyre</t>
+          <t>claystone</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2123,7 +2123,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>phlogopite</t>
+          <t>tailings ("red mud")</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2133,7 +2133,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tailings ("red mud")</t>
+          <t>chert</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -2143,7 +2143,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>sandstone(?)</t>
+          <t>malignite</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -2153,7 +2153,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>quartz pebble conglomerate</t>
+          <t>quartz porphyry</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -2163,7 +2163,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>metamorphosed mafic volcanic rock</t>
+          <t>fluvial sediments</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -2173,7 +2173,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>malignite</t>
+          <t>alaskite</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -2183,7 +2183,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>silica breccia</t>
+          <t>carbonatite tuff</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -2193,7 +2193,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>iron oxide rock</t>
+          <t>black sand</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -2213,7 +2213,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>volcanics</t>
+          <t>banded carbonates</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -2223,7 +2223,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>saprolite</t>
+          <t>unconsolidated gravel</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -2233,7 +2233,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>eluvial and alluvial sediments</t>
+          <t>nephelinite</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -2243,7 +2243,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>quartz porphyry</t>
+          <t>carbonaceous sand</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -2253,27 +2253,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>chert</t>
+          <t>hornfels</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>unconsolidated gravel</t>
+          <t>silicified quartz sandstone</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>alkaline ultramafic rock</t>
+          <t>alluvial</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -2283,7 +2283,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>peralkaline rhyolite</t>
+          <t>fluvial sands</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -2293,7 +2293,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>peralkaline nepheline syenite</t>
+          <t>granite breccia</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -2303,7 +2303,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>flint</t>
+          <t>adamellite</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -2313,7 +2313,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>weathered calcite carbonatite</t>
+          <t>colluvium</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -2323,7 +2323,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>coal</t>
+          <t>peralkaline quartz syenite</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -2333,7 +2333,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>alluvial</t>
+          <t>other metasediments</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -2343,7 +2343,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>carbonate rock</t>
+          <t>trachyandesite</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -2353,7 +2353,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>carbonaceous sandstone</t>
+          <t>lamprophyre</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -2363,7 +2363,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>trachyandesite</t>
+          <t>metamorphic rocks</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -2373,7 +2373,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>fluvial sands</t>
+          <t>silt</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -2383,7 +2383,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>pebble conglomerate</t>
+          <t>dunite</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -2393,7 +2393,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>river sand</t>
+          <t>dolomitic carbonaceous rock</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -2403,7 +2403,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>continental sand</t>
+          <t>mafic syenite</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -2413,7 +2413,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>hornfels</t>
+          <t>river sand</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -2423,7 +2423,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>silt</t>
+          <t>granitoid; metasediment</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -2433,7 +2433,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>undifferentiated sediments</t>
+          <t>malignite–ijolite</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -2443,7 +2443,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>regolith</t>
+          <t>biotite gneiss</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -2453,7 +2453,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>colluvium</t>
+          <t>hydrothermal silicified and hematitic breccia</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -2463,7 +2463,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>altered microgranite and quartz alkali-feldspar syenite</t>
+          <t>miaskite</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -2473,7 +2473,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>alkaline trachyte</t>
+          <t>melilitolite</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -2483,7 +2483,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>rodbergite</t>
+          <t>arkosic gneiss</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -2493,7 +2493,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>arkosic gneiss</t>
+          <t>granite-granodiorite(?)</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -2503,7 +2503,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>volcanic breccia</t>
+          <t>alluvial sediments</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -2513,7 +2513,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>alkivite</t>
+          <t>altered volcanic rock and granite</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -2523,7 +2523,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>magnesiocarbonatite</t>
+          <t>magnetite rock</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -2533,7 +2533,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>larvikite</t>
+          <t>eudialytic lujavrite</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -2543,7 +2543,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>syenogranite</t>
+          <t>urtite-melteigite-jacupirangite</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -2553,7 +2553,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>miaskite</t>
+          <t>syenogranite</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -2563,7 +2563,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>urtite-melteigite-jacupirangite</t>
+          <t>carbonatite dikes</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -2573,7 +2573,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>magnetite rock</t>
+          <t>kaolinite</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -2583,7 +2583,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>metamorphosed mica schist</t>
+          <t>sand and clay</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -2593,7 +2593,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>calcite and dolomite carbonatite</t>
+          <t>meta-arkose</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -2603,7 +2603,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>granite-granodiorite(?)</t>
+          <t>larvikite</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -2613,7 +2613,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kaolinite</t>
+          <t>rhyolite tuff</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -2623,7 +2623,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>apatite-magnetite rock</t>
+          <t>glacial outwash</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -2633,7 +2633,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>melilitolite</t>
+          <t>metamorphosed mica schist</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -2643,7 +2643,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sovite</t>
+          <t>altered microgranite and quartz alkali-feldspar syenite</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -2653,7 +2653,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>malignite–ijolite</t>
+          <t>sovite</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -2663,7 +2663,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>microgranite</t>
+          <t>magnesiocarbonatite</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -2673,7 +2673,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>tuffite</t>
+          <t>alkaline trachyte</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -2683,7 +2683,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>miarolitic granite</t>
+          <t>alkaline ultramafic rock</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -2693,7 +2693,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>dunite</t>
+          <t>alkivite</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -2703,7 +2703,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>altered volcanic rock and granite</t>
+          <t>tuffite</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -2713,7 +2713,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>eudialytic lujavrite</t>
+          <t>miarolitic granite</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -2723,7 +2723,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>biotite gneiss</t>
+          <t>carbonaceous sandstone</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -2733,7 +2733,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sand and clay</t>
+          <t>undifferentiated sediments</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -2743,7 +2743,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>nepheline gneiss</t>
+          <t>regolith</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -2753,7 +2753,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>deltaic sediments(?)</t>
+          <t>microgranite</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -2763,7 +2763,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>aegirine-augite syenite</t>
+          <t>peralkaline rhyolite</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -2773,7 +2773,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>alluvial sediments</t>
+          <t>aegirine-augite syenite</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -2783,7 +2783,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>granite breccia</t>
+          <t>calcite and dolomite carbonatite</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -2793,7 +2793,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>alvikite</t>
+          <t>agpaitic nepheline syenite</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -2801,11 +2801,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>agpaitic nepheline syenite</t>
-        </is>
-      </c>
+      <c r="A238" t="inlineStr"/>
       <c r="B238" t="n">
         <v>2</v>
       </c>
@@ -2813,7 +2809,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>peralkaline quartz syenite</t>
+          <t>alvikite</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -2823,7 +2819,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kaolinite mudstone</t>
+          <t>weathered basalt</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -2833,7 +2829,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>weathered basalt</t>
+          <t>weathered dolomitic carbonatite</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -2843,7 +2839,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>metamorphic rocks</t>
+          <t>weathered calcite carbonatite</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -2853,7 +2849,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>granite pegmatite</t>
+          <t>peralkaline nepheline syenite</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -2863,7 +2859,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>carbonate</t>
+          <t>pebble conglomerate</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -2873,7 +2869,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>black slate</t>
+          <t>alkali syenite</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -2883,7 +2879,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>alkali syenite</t>
+          <t>nepheline gneiss</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -2893,7 +2889,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>other metasediments</t>
+          <t>carbonate rock</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -2903,7 +2899,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>glacial outwash</t>
+          <t>schist breccia</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -2913,7 +2909,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>lamprophyre</t>
+          <t>volcanic breccia</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -2923,7 +2919,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>mafic syenite</t>
+          <t>sand and gravel</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -2933,7 +2929,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>sand and gravel</t>
+          <t>granitic pegmatite</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -2943,7 +2939,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>adamellite</t>
+          <t>flint</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -2953,7 +2949,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>marlstone</t>
+          <t>coal</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -2963,7 +2959,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ignimbrite</t>
+          <t>apatite-magnetite rock</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -2973,7 +2969,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>carbonatitic breccia</t>
+          <t>weathered dolomite</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -2983,7 +2979,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>granitoid; metasediment</t>
+          <t>continental sand</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -2993,7 +2989,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>carbonatite agglomerate</t>
+          <t>granite pegmatite</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -3003,7 +2999,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>weathered dolomitic carbonatite</t>
+          <t>muscovite granite</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -3013,7 +3009,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>phosphate rock</t>
+          <t>granite greisen</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -3023,7 +3019,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>dolomitic carbonaceous rock</t>
+          <t>kaolinite mudstone</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -3033,7 +3029,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>weathered dolomite</t>
+          <t>marlstone</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -3043,7 +3039,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>coaly shale</t>
+          <t>phosphate rock</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -3053,7 +3049,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>felsic igneous or sedimentary rock (inferred</t>
+          <t>ignimbrite</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -3063,7 +3059,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>granitic pegmatite</t>
+          <t>black slate</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -3073,7 +3069,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>rhyolite tuff</t>
+          <t>tinguaite</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -3083,7 +3079,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>hydrothermal silicified and hematitic breccia</t>
+          <t>carbonatite agglomerate</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -3093,7 +3089,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>muscovite granite</t>
+          <t>rodbergite</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -3103,7 +3099,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>tinguaite</t>
+          <t>carbonate</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -3113,7 +3109,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>carbonatite dikes</t>
+          <t>deltaic sediments(?)</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -3123,7 +3119,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>schist breccia</t>
+          <t>carbonatitic breccia</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -3133,7 +3129,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>granite greisen</t>
+          <t>coaly shale</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -3143,33 +3139,37 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>meta-arkose</t>
+          <t>biotite syenite</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr"/>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>sediments OR pegmatite</t>
+        </is>
+      </c>
       <c r="B273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>silicified quartz sandstone</t>
+          <t>beach ridge sand</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>carbonate veins and dikes</t>
+          <t>granite OR arenaceous sand and clay sediments</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -3179,7 +3179,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>alkaline pegmatite in dunite</t>
+          <t>arenaceous sand and clay sediments</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -3189,7 +3189,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>essexite</t>
+          <t>tailings</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -3199,7 +3199,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>alkalic ultramafic carbonatite</t>
+          <t>alluvial gravel</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -3209,7 +3209,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>granitoids</t>
+          <t>mica schist(?)</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -3219,7 +3219,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>alkalic volcanic rock</t>
+          <t>spodumene-granite porphyry</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -3229,7 +3229,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>dolostone</t>
+          <t>sediments or skarn</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -3239,7 +3239,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>alkaline pegmatites</t>
+          <t>biotite porphyry granite</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -3249,7 +3249,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>alkaline and peralkaline syenites</t>
+          <t>volcanic(?) breccia</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -3259,7 +3259,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>grorudite</t>
+          <t>felsic intrusions</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -3269,7 +3269,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>limestone; lesser shale</t>
+          <t>felsic rhyolite</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -3279,7 +3279,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>metasomatic carbonate</t>
+          <t>weathered calcite and dolomite carbonatite</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -3289,7 +3289,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>calcitic carbonatite</t>
+          <t>granite or marl</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -3299,7 +3299,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>lamprophyre and phonolite dikes</t>
+          <t>weathered calcite and ankerite carbonatite</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -3309,7 +3309,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ultramafic rock</t>
+          <t>arenite</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -3319,7 +3319,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>apatite-forsterite rock</t>
+          <t>marine sand; continental sand</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -3329,7 +3329,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ultramafic-alkaline rock</t>
+          <t>ultramafic rock</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -3339,7 +3339,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>hydrothermal carbonatite</t>
+          <t>calc-silicate metasediments</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -3349,7 +3349,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>alkalic granitic stock</t>
+          <t>intermediate intrusions OR sediments</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -3359,7 +3359,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>rapakivi and alkali granite</t>
+          <t>fluvioglacial sediments</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -3369,7 +3369,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>dolomite and calcite carbonatite</t>
+          <t>and phyllitic shale</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -3379,7 +3379,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>gabbroid</t>
+          <t>dikes</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -3389,7 +3389,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>granulite</t>
+          <t>mafic-ultramafic metavolcanic rock</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -3399,7 +3399,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>okaite</t>
+          <t>laterized sediments</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -3409,7 +3409,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>pegmatites in schist</t>
+          <t>graphitic slate</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -3419,7 +3419,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>phosphatic phyllite</t>
+          <t>metavolcanics</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -3429,7 +3429,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>weathered dolomite and calcite carbonatite</t>
+          <t>alluvial-fluvial sand</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -3439,7 +3439,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>metasomatic rock</t>
+          <t>beach sand(?)</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -3449,7 +3449,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>leucogranite(?)</t>
+          <t>marl</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -3459,7 +3459,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kimberlite</t>
+          <t>carbonaceous</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -3469,7 +3469,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>lapilli tuff</t>
+          <t>siliceous</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -3479,7 +3479,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>syenite porphyry</t>
+          <t>beach and paleodune sand</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -3489,7 +3489,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>apatite rock</t>
+          <t>ironstone</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -3499,7 +3499,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>juvite</t>
+          <t>camptonite</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -3509,7 +3509,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>apatite-nepheline rock</t>
+          <t>alluvial and colluvial sediment</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -3519,7 +3519,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>phlogopite glimmerite</t>
+          <t>"basement rocks"</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -3529,7 +3529,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>granitoid</t>
+          <t>calcite-amphibole-pyroxene rock</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -3539,7 +3539,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>apatite-dolomite carbonatite</t>
+          <t>Eolian sand</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -3549,7 +3549,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>lepidomelane granite</t>
+          <t>intermediate intrusions or granite</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -3559,7 +3559,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>aegirine-arfvedsonite granite</t>
+          <t>clayey sand</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -3569,7 +3569,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>quartz-hematite-muscovite (illite) metasomatite</t>
+          <t>domes</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -3579,7 +3579,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>greywacke</t>
+          <t>uranium tailings</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -3589,7 +3589,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>peraluminous pegmatitic granite in calc-silicate horizons</t>
+          <t>rhyolite porphyry</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -3599,7 +3599,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>carbonate veins</t>
+          <t>marine sand</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -3609,7 +3609,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>fluvioglacial sediments</t>
+          <t>peralkaline metasomatite(?)</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -3619,7 +3619,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>clayey sand</t>
+          <t>alkaline lamprophyre</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -3629,7 +3629,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>beach sand and clay sand</t>
+          <t>alkalic volcanic rock</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -3639,7 +3639,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>trondhjemite to granodiorite</t>
+          <t>phosphatic phyllite</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -3649,7 +3649,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>(hornblende) quartz monzodiorite to biotite granodiorite</t>
+          <t>lapilli tuff</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -3659,7 +3659,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>silicified and brecciated sandstone</t>
+          <t>monzogranitic rock</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -3669,7 +3669,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>uranium tailings</t>
+          <t>kimberlite</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -3679,7 +3679,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>rhyolite porphyry</t>
+          <t>carbonate-rich lamprophyre</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -3689,7 +3689,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>alkaline volcanic rock</t>
+          <t>carbonate veins and dikes</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -3699,7 +3699,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ironstone</t>
+          <t>dolostone</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -3709,7 +3709,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>agpaitic phonolite</t>
+          <t>pebbles</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -3719,7 +3719,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>hematitic breccia</t>
+          <t>limestone; lesser shale</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -3729,7 +3729,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>brecciated gneiss and granite</t>
+          <t>melasyenite to melagranite</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -3739,7 +3739,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Eolian sand</t>
+          <t>syenitic fenite</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -3749,7 +3749,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>alkali lamprophyre</t>
+          <t>lamprophyre and phonolite dikes</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -3759,7 +3759,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>eudialyte granite</t>
+          <t>greywacke</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -3769,7 +3769,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>dune</t>
+          <t>juvite</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -3779,7 +3779,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>and beach ridge sand</t>
+          <t>pegmatites in schist</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -3789,7 +3789,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>fenitized peralkaline arfvedsonite-aegirine granite and associated agpaitic pegmatites</t>
+          <t>phosphoritic conglomerate</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -3799,7 +3799,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>altered alkaline trachyte</t>
+          <t>okaite</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -3809,7 +3809,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>beach ridge sand</t>
+          <t>granulite</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -3819,7 +3819,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>pebbles</t>
+          <t>peralkaline flow</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -3829,7 +3829,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>tailings</t>
+          <t>monzonite (larvikite)</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -3839,7 +3839,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>calc-silicate metasediments</t>
+          <t>metagabbro</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -3849,7 +3849,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>volcanic(?) breccia</t>
+          <t>hematite-rich diatreme breccia</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -3859,7 +3859,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>hematite breccia</t>
+          <t>peralkaline intrusion</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -3869,7 +3869,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>"basement rocks"</t>
+          <t>syenite breccia</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -3879,7 +3879,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>pegmatite in peralkaline granite</t>
+          <t>nepheline sodalite syenite</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -3889,7 +3889,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>biotite syenite</t>
+          <t>migmatitic gneiss</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -3899,7 +3899,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>alkaline ultrabasic rocks</t>
+          <t>nepheline diorite and monzonite</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -3909,7 +3909,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>phosphatic shale</t>
+          <t>anorthositic gabbro</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -3919,7 +3919,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>stockworks</t>
+          <t>bioclastic phosphorite</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -3929,7 +3929,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>carbonatite / alkaline igneous (inferred</t>
+          <t>breccias</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -3939,7 +3939,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>weathered calcite and ankerite carbonatite</t>
+          <t>sideritic carbonatite</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -3949,7 +3949,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>comenditic flows and peralkaline ignimbrites</t>
+          <t>carbonate veins</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -3959,7 +3959,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>aeolian sand</t>
+          <t>pegmatite in peralkaline granite</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -3969,7 +3969,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>marine sand</t>
+          <t>phosphatic shale</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -3979,7 +3979,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>biotite porphyry granite</t>
+          <t>(hornblende) quartz monzodiorite to biotite granodiorite</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -3989,7 +3989,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>spodumene-granite porphyry</t>
+          <t>altered alkaline trachyte</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -3999,7 +3999,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>alkaline rocks</t>
+          <t>nepheline syenite(?)</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -4009,7 +4009,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>weathered eudialyte granite</t>
+          <t>and beach ridge sand</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -4019,7 +4019,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>alluvial and colluvial sediment</t>
+          <t>monzodiorite-syenite stock</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -4029,7 +4029,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>calcite-amphibole-pyroxene rock</t>
+          <t>banded iron formation</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -4039,7 +4039,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>mica schist(?)</t>
+          <t>quartz syenite porphyry</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -4049,7 +4049,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>limestone; clay; red sandstones</t>
+          <t>dune</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -4059,7 +4059,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>theralite</t>
+          <t>quartz-feldspar schist</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -4069,7 +4069,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>mafic-ultramafic metavolcanic rock</t>
+          <t>brecciated gneiss and granite</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -4079,7 +4079,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>migmatite—hornblende gneiss</t>
+          <t>hematitic breccia</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -4089,7 +4089,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>laterized sediments</t>
+          <t>diabase</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -4099,7 +4099,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>metavolcanics</t>
+          <t>calcareous sedimentary rock</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -4109,7 +4109,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>alluvial-fluvial sand</t>
+          <t>alkaline volcanic rock</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -4119,7 +4119,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>beach sand(?)</t>
+          <t>silicified and brecciated sandstone</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -4129,7 +4129,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>beach and paleodune sand</t>
+          <t>topaz granite</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -4139,7 +4139,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>nepheline syenite dikes</t>
+          <t>pyroclastic rock</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -4149,7 +4149,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>tinguaite dikes</t>
+          <t>trondhjemite to granodiorite</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -4159,7 +4159,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>alkali metasomatite</t>
+          <t>beach sand and clay sand</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -4169,7 +4169,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>felsic rhyolite</t>
+          <t>intermediate igneous rock</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -4179,7 +4179,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>granite or intermediate intrusion</t>
+          <t>syenodiorite</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -4189,7 +4189,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>intermediate intrusions or albitite</t>
+          <t>hematite breccia</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -4199,7 +4199,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>quartz syenite porphyry</t>
+          <t>weathered peridotite</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -4209,7 +4209,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>andesite-dacite</t>
+          <t>and  limestone</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -4219,7 +4219,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>marine sand; continental sand</t>
+          <t>allanite gneiss</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -4229,7 +4229,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>arenite</t>
+          <t>syenite(?)</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -4239,7 +4239,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>granite or marl</t>
+          <t>volcano-sedimentary rock</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -4249,7 +4249,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>felsic intrusions</t>
+          <t>alkaline rocks</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -4259,7 +4259,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>moderately to strongly hematized nepheline syenite</t>
+          <t>peraluminous pegmatitic granite in calc-silicate horizons</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -4269,7 +4269,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>domes</t>
+          <t>aeolian sand</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -4279,7 +4279,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>dikes</t>
+          <t>comenditic flows and peralkaline ignimbrites</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -4289,7 +4289,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>graphitic slate</t>
+          <t>andesite-dacite</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -4299,7 +4299,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>marl</t>
+          <t>metasomatic carbonate</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -4309,7 +4309,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>carbonaceous</t>
+          <t>stockworks</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -4319,7 +4319,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>siliceous</t>
+          <t>highly weathered lujavrite and khibinite</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -4329,7 +4329,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>and phyllitic shale</t>
+          <t>albite-rich granite</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -4339,7 +4339,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>granite porphyry dike</t>
+          <t>weathered nepheline syenite and phonolite</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -4349,7 +4349,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>garnet-nepheline syenite</t>
+          <t>weathered tinguaite</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -4359,7 +4359,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>biotite-albite granite</t>
+          <t>lateritic saprolite</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -4369,7 +4369,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>sandstone or granite?</t>
+          <t>tinguaite(?)</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -4379,7 +4379,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>shaly clay</t>
+          <t>probably alkaline-ultrabasic intrusions</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -4389,7 +4389,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>greisenized granite</t>
+          <t>altered granite and comendite; marble</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -4399,7 +4399,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>bone detritus</t>
+          <t>nepheline-aegirine syenite</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -4409,7 +4409,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>metasediments: limestone</t>
+          <t>tinguaite dikes</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -4419,7 +4419,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>peat</t>
+          <t>carbonaceous siltstone</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -4429,7 +4429,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>marine clay</t>
+          <t>weathered nepheline syenite</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -4439,7 +4439,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>bone debris</t>
+          <t>hyperbasite</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -4449,7 +4449,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>granite or carbonaceous sand</t>
+          <t>metasedimentary and metaphyroclastic rock</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -4459,7 +4459,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>limestone breccia</t>
+          <t>mafic metavolcanic rock</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -4469,7 +4469,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>argillite</t>
+          <t>coastal dune sand</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -4479,7 +4479,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>arenaceous sediments</t>
+          <t>leucogranite; sedimentary rocks</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -4489,7 +4489,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>granite porphyry dikes</t>
+          <t>feldspathic carbonatite</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -4499,7 +4499,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>rhyolitic tuff</t>
+          <t>aplite pegmatite</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -4509,7 +4509,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>silicified granophyre</t>
+          <t>gneiss; schist</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -4519,7 +4519,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>leucosyenite</t>
+          <t>grit</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -4529,7 +4529,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>leucosyenite or granite?</t>
+          <t>silcrete</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -4539,7 +4539,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>intermediate intrusions or granite</t>
+          <t>saprolite-laterite</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -4549,7 +4549,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>intermediate intrusions OR sediments</t>
+          <t>and dikes</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -4559,7 +4559,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>sediments or skarn</t>
+          <t>gabbro-diorite</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -4569,7 +4569,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>monzogranitic rock</t>
+          <t>carbonatite lava</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -4579,7 +4579,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>allanite gneiss</t>
+          <t>melansyenite dike</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -4589,7 +4589,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>syenite(?)</t>
+          <t>serpentinized peridotite</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -4599,7 +4599,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>volcano-sedimentary rock</t>
+          <t>andesitic porphyry</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -4609,7 +4609,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>pyroclastic rock</t>
+          <t>lepidomelane syenite</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -4619,7 +4619,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>syenitic fenite</t>
+          <t>biotite syenogranite</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -4629,7 +4629,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>melasyenite to melagranite</t>
+          <t>phonolite; bauxite</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -4639,7 +4639,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>carbonate-rich lamprophyre</t>
+          <t>alkaline ultrabasic rocks</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -4649,7 +4649,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>phosphoritic conglomerate</t>
+          <t>deltaic and alluvial sediments</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -4659,7 +4659,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>granite OR arenaceous sand and clay sediments</t>
+          <t>sand dunes</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -4669,7 +4669,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>peralkaline flow</t>
+          <t>chlorite-biotite schist</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -4679,7 +4679,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>monzonite (larvikite)</t>
+          <t>ferro carbonatite</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -4689,7 +4689,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>metagabbro</t>
+          <t>beach sands and dunes</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -4699,7 +4699,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>peralkaline intrusion</t>
+          <t>garnet-muscovite schist</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -4709,7 +4709,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>migmatitic gneiss</t>
+          <t>quartzite and brecciated quartzite</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -4719,7 +4719,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>bioclastic phosphorite</t>
+          <t>epidiorite</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -4729,7 +4729,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>sideritic carbonatite</t>
+          <t>riebeckite carbonatite</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -4739,7 +4739,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>alkaline igneous or carbonatite (inferred</t>
+          <t>siderite-ankerite-hematite carbonatite</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -4749,7 +4749,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>and  limestone</t>
+          <t>riebeckite syenite</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -4759,7 +4759,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>weathered peridotite</t>
+          <t>barite-strontianite alvikite</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -4769,7 +4769,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>syenodiorite</t>
+          <t>pyroclastic carbonatite</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -4779,7 +4779,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>arenaceous sand and clay sediments</t>
+          <t>ultramafic rock; granite</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -4789,7 +4789,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>sediments OR pegmatite</t>
+          <t>granodioritic to tonalitic gneiss</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -4799,7 +4799,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>alluvial gravel</t>
+          <t>alkali metasomatic rock</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -4809,7 +4809,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>weathered calcite and dolomite carbonatite</t>
+          <t>agpaitic nepheline syenite complex</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -4819,7 +4819,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>camptonite</t>
+          <t>oligoclasite</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -4829,7 +4829,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>alkaline lamprophyre</t>
+          <t>bauxitic clay</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -4839,7 +4839,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>nepheline syenite(?)</t>
+          <t>amphibolite- and granulite-facies metamorphic rocks</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -4849,7 +4849,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>monzodiorite-syenite stock</t>
+          <t>nepheline phonolite</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -4859,7 +4859,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>banded iron formation</t>
+          <t>porphyritic arfvedsonite</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -4869,7 +4869,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>peralkaline metasomatite(?)</t>
+          <t>sandstone; metasemipelites</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -4879,7 +4879,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>quartz-feldspar schist</t>
+          <t>coastal-lacustrine sediments</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -4889,7 +4889,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>diabase</t>
+          <t>igneous or hydrothermal rock (inferred</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -4899,7 +4899,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>calcareous sedimentary rock</t>
+          <t>greenstone</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -4909,7 +4909,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>topaz granite</t>
+          <t>fenetized monzogranite</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -4919,7 +4919,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>intermediate igneous rock</t>
+          <t>phosphatic conglomerate</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -4929,7 +4929,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>volcanic rocks</t>
+          <t>phosphatic glauconitic sandstone</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -4939,7 +4939,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>weathered quartzite</t>
+          <t>polymictic conglomerate</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -4949,7 +4949,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>quartz-microcline-albite metasomatite</t>
+          <t>monchiquite</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -4959,7 +4959,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>probably alkaline-ultrabasic intrusions</t>
+          <t>liebenerite syenite</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -4969,7 +4969,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>coastal dune sand</t>
+          <t>continental sand and gravel</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -4979,7 +4979,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>mafic metavolcanic rock</t>
+          <t>weathered quartzite</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -4989,7 +4989,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>metasedimentary and metaphyroclastic rock</t>
+          <t>syenite porphyry</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -4999,7 +4999,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>weathered nepheline syenite</t>
+          <t>apatite rock</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -5009,7 +5009,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>syenite breccia</t>
+          <t>granite porphyry dikes</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -5019,7 +5019,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>nepheline-aegirine syenite</t>
+          <t>apatite-nepheline rock</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -5029,7 +5029,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>altered granite and comendite; marble</t>
+          <t>phlogopite glimmerite</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -5039,7 +5039,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>tinguaite(?)</t>
+          <t>granitoid</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -5049,7 +5049,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>aplite pegmatite</t>
+          <t>apatite-dolomite carbonatite</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -5059,7 +5059,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>lateritic saprolite</t>
+          <t>lepidomelane granite</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -5069,7 +5069,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>weathered tinguaite</t>
+          <t>aegirine-arfvedsonite granite</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -5079,7 +5079,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>weathered nepheline syenite and phonolite</t>
+          <t>quartz-hematite-muscovite (illite) metasomatite</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -5089,7 +5089,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>albite-rich granite</t>
+          <t>rhyolitic tuff</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -5099,7 +5099,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>biotite syenogranite</t>
+          <t>apatite-forsterite rock</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -5109,7 +5109,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>highly weathered lujavrite and khibinite</t>
+          <t>silicified granophyre</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -5119,7 +5119,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>phonolite; bauxite</t>
+          <t>essexite</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -5129,7 +5129,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>feldspathic carbonatite</t>
+          <t>alkaline pegmatite in dunite</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -5139,7 +5139,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>grit</t>
+          <t>leucosyenite</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -5149,7 +5149,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>liebenerite syenite</t>
+          <t>granitoids</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -5159,7 +5159,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>weathered ankerite carbonatite (sövitic)</t>
+          <t>leucosyenite or granite?</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -5169,7 +5169,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>metasomatically altered granitic rock</t>
+          <t>limestone breccia</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -5179,7 +5179,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>calcite-dolomite carbonatite</t>
+          <t>garnet-nepheline syenite</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -5189,7 +5189,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>alkaline metasomatite</t>
+          <t>coastal deltaic plain sediments</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -5199,7 +5199,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>some pyroxenite</t>
+          <t>granite porphyry dike</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -5209,7 +5209,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>plagioclase-apatite-clinopyroxene rock; clinopyroxene-bearing syenite; monzonite; mangerite; pelitic</t>
+          <t>alkalic ultramafic carbonatite</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -5219,7 +5219,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>quartzitic and calcsilicate gneiss and granulite; mafic to ultramafic igneous rocks</t>
+          <t>calcitic carbonatite</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -5229,7 +5229,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>ferricrete</t>
+          <t>grorudite</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -5239,7 +5239,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>magmatic breccia</t>
+          <t>granite or intermediate intrusion</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -5249,7 +5249,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>silcrete</t>
+          <t>alkaline and peralkaline syenites</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -5259,7 +5259,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>continental sand and gravel</t>
+          <t>alkaline pegmatites</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -5269,7 +5269,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>monchiquite</t>
+          <t>intermediate intrusions or albitite</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -5279,7 +5279,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>serpentinized peridotite</t>
+          <t>arenaceous sediments</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -5289,7 +5289,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>melansyenite dike</t>
+          <t>leucogranite(?)</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -5299,7 +5299,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>carbonatite lava</t>
+          <t>argillite</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -5309,7 +5309,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>and dikes</t>
+          <t>metasomatically altered granitic rock</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -5319,7 +5319,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>saprolite-laterite</t>
+          <t>biotite-albite granite</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -5329,7 +5329,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>deltaic and alluvial sediments</t>
+          <t>magmatic breccia</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -5339,7 +5339,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>polymictic conglomerate</t>
+          <t>volcanic rocks</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -5349,7 +5349,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>fenetized monzogranite</t>
+          <t>shaly clay</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -5359,7 +5359,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>phosphatic conglomerate</t>
+          <t>weathered ankerite carbonatite (sövitic)</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -5369,7 +5369,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>alkali metasomatic rock</t>
+          <t>greisenized granite</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -5379,7 +5379,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>oligoclasite</t>
+          <t>bone detritus</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -5389,7 +5389,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>bauxitic clay</t>
+          <t>metasediments: limestone</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -5399,7 +5399,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>amphibolite- and granulite-facies metamorphic rocks</t>
+          <t>quartzitic and calcsilicate gneiss and granulite; mafic to ultramafic igneous rocks</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -5409,7 +5409,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>porphyritic arfvedsonite</t>
+          <t>plagioclase-apatite-clinopyroxene rock; clinopyroxene-bearing syenite; monzonite; mangerite; pelitic</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -5419,7 +5419,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>coastal-lacustrine sediments</t>
+          <t>some pyroxenite</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -5429,7 +5429,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>beforsitic carbonatite</t>
+          <t>alkaline metasomatite</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -5439,7 +5439,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>phosphatic glauconitic sandstone</t>
+          <t>calcite-dolomite carbonatite</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -5449,7 +5449,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>magnetite carbonatite</t>
+          <t>quartz-microcline-albite metasomatite</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -5459,7 +5459,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>carbonaceous siltstone</t>
+          <t>ultramafic-alkaline rock</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -5469,7 +5469,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>hyperbasite</t>
+          <t>peat</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -5479,7 +5479,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>leucogranite; sedimentary rocks</t>
+          <t>alkali metasomatite</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -5489,7 +5489,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>gneiss; schist</t>
+          <t>marine clay</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -5499,7 +5499,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>gabbro-diorite</t>
+          <t>alkali lamprophyre</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -5509,7 +5509,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>andesitic porphyry</t>
+          <t>bone debris</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -5519,7 +5519,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>lepidomelane syenite</t>
+          <t>alkalic granitic stock</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -5529,7 +5529,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>riebeckite syenite</t>
+          <t>rapakivi and alkali granite</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -5539,7 +5539,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>riebeckite carbonatite</t>
+          <t>dolomite and calcite carbonatite</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -5549,7 +5549,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>epidiorite</t>
+          <t>gabbroid</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -5559,7 +5559,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>quartzite and brecciated quartzite</t>
+          <t>sandstone or granite?</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -5569,7 +5569,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>greenstone</t>
+          <t>granite or carbonaceous sand</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -5579,7 +5579,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>igneous or hydrothermal rock (inferred</t>
+          <t>weathered dolomite and calcite carbonatite</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -5589,7 +5589,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>nepheline phonolite</t>
+          <t>metasomatic rock</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -5599,7 +5599,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>agpaitic nepheline syenite complex</t>
+          <t>aplitic granite</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -5609,7 +5609,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>granodioritic to tonalitic gneiss</t>
+          <t>alkali granite and volcanics</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -5619,7 +5619,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>ultramafic rock; granite</t>
+          <t>arfvedsonite gneiss</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -5629,7 +5629,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>pyroclastic carbonatite</t>
+          <t>carbonate rocks</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -5639,7 +5639,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>barite-strontianite alvikite</t>
+          <t>leucitite</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -5649,7 +5649,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>siderite-ankerite-hematite carbonatite</t>
+          <t>basic and ultrabasic rocks</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -5659,7 +5659,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>beach sands and dunes</t>
+          <t>aegirine alkaline granite</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -5669,7 +5669,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>ferro carbonatite</t>
+          <t>arfvedsonite syenite</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -5679,7 +5679,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>chlorite-biotite schist</t>
+          <t>siliceous dolomite</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -5689,7 +5689,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>sand dunes</t>
+          <t>brucite marble</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -5699,7 +5699,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>coastal deltaic plain sediments</t>
+          <t>alkaline dunite</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -5709,7 +5709,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>garnet-muscovite schist</t>
+          <t>aegerine nepheline syenite</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -5719,7 +5719,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>hematite-rich diatreme breccia</t>
+          <t>metasediments and metavolcanics—marble</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -5729,7 +5729,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>and schist</t>
+          <t>gray to black shale</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -5739,7 +5739,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>nepheline sodalite syenite</t>
+          <t>dolomicrite</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -5749,7 +5749,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>magnetite-apatite rock</t>
+          <t>monzonitic granite</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -5759,7 +5759,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>albite metasomatite</t>
+          <t>porphyry</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -5769,7 +5769,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>albite-polylithionite-trilithionite granite</t>
+          <t>aegirine granite</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -5779,7 +5779,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>microcline (amazonite)-albite granite</t>
+          <t>nordmarkite(?)</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -5789,7 +5789,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>pantellerite dikes</t>
+          <t>biotite-calcite schist</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -5799,7 +5799,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>riebeckite-arfvedsonite granite</t>
+          <t>and lava</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -5809,7 +5809,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>subalkaline granite</t>
+          <t>volcanic carbonatite lapilli tuff</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -5819,7 +5819,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>leucocratic trachyte</t>
+          <t>ferromanganous carbonate</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -5829,7 +5829,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>potassic alkaline volcanic rocks</t>
+          <t>magnetic quartzite</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -5839,7 +5839,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>nepheline diorite and monzonite</t>
+          <t>terra rossa</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -5849,7 +5849,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>melanephelinite</t>
+          <t>basic-ultrabasic lamprophyre</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -5859,7 +5859,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>melaleucitite</t>
+          <t>ultramafic rocks: pyroxene</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -5869,7 +5869,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>mafic gneiss</t>
+          <t>felsic schist</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -5879,7 +5879,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>alkaline riebeckite syenite</t>
+          <t>biotite monzonite granite</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -5889,7 +5889,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>stream sediment</t>
+          <t>alkaline granite porphyry</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -5899,7 +5899,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>metatrachytic rock</t>
+          <t>rhyolite flow and tuff</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -5909,7 +5909,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>chlorite-muscovite (sericite)-quartz schist</t>
+          <t>alaskite with xenoliths of metamorphic rock</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -5919,7 +5919,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>peralkaline pyroxenite</t>
+          <t>aegirinolite</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -5929,7 +5929,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>biotite-amphibole schist  amphibolite</t>
+          <t>aegerine-syenite dikes</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -5939,7 +5939,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>leucocratic muscovite granite</t>
+          <t>nepheline-aegerine rock</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -5949,7 +5949,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>channel sand</t>
+          <t>dolomitic phosphorite</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -5959,7 +5959,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>magnetite-microcline rock</t>
+          <t>metavolcanic rocks-spilite</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -5969,7 +5969,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>siderite sövite</t>
+          <t>keratophyre</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -5979,7 +5979,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>siliceous sediments</t>
+          <t>keratophyre volcaniclastic rock</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -5989,7 +5989,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>marble (carbonatite)</t>
+          <t>carbonatite and pyroxenite breccia</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -5999,7 +5999,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>lava</t>
+          <t>leptite</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -6009,7 +6009,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>basic tuff</t>
+          <t>muscovite–tourmaline granite</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -6019,7 +6019,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>alkaline basalt</t>
+          <t>melaleucitite</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -6029,7 +6029,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>trachyphonolite</t>
+          <t>pantellerite dikes</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -6039,7 +6039,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>slate; alluvial sediments</t>
+          <t>riebeckite-arfvedsonite granite</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -6049,7 +6049,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>colluvial</t>
+          <t>subalkaline granite</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -6059,7 +6059,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>and residual sediments</t>
+          <t>leucocratic trachyte</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -6069,7 +6069,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>(hornblende) granodiorite</t>
+          <t>magnetite-apatite rock</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -6079,7 +6079,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>biotite granodiorite</t>
+          <t>potassic alkaline volcanic rocks</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -6089,7 +6089,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>biotite-(hornblende) granodiorite</t>
+          <t>melanephelinite</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -6099,7 +6099,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>feldspathic breccias</t>
+          <t>alkaline riebeckite syenite</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -6109,7 +6109,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>metasyenite dike</t>
+          <t>leptynite</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -6119,7 +6119,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>tourmaline-muscovite granite</t>
+          <t>stream sediment</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -6129,7 +6129,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>metasedimentary rock</t>
+          <t>metatrachytic rock</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -6139,7 +6139,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>topaz-bearing granite</t>
+          <t>chlorite-muscovite (sericite)-quartz schist</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -6149,7 +6149,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>meta-norite</t>
+          <t>metasyenite dike</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -6159,7 +6159,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>hematite carbonatite (rodberg)</t>
+          <t>tourmaline-muscovite granite</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -6169,7 +6169,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>felsic metavolcanic rocks</t>
+          <t>metasedimentary rock</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -6179,7 +6179,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>albite gneiss</t>
+          <t>roof pendants–calcic marble</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -6189,7 +6189,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>aegirine-riebeckite gneiss</t>
+          <t>microcline (amazonite)-albite granite</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -6199,7 +6199,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>magnetite-carbonate rock</t>
+          <t>albite-polylithionite-trilithionite granite</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -6209,7 +6209,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>mangerite</t>
+          <t>albite metasomatite</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -6219,7 +6219,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>siderite carbonatite</t>
+          <t>peralkaline pyroxenite</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -6229,7 +6229,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>sandy siltstone</t>
+          <t>magnetite-microcline rock</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -6239,7 +6239,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>metatrachydacite</t>
+          <t>siliceous sediments</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -6249,7 +6249,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>carbonate-sericite-schist</t>
+          <t>marble (carbonatite)</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -6259,7 +6259,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>iron ore</t>
+          <t>lava</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -6269,7 +6269,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>metavolcanic rock(?)</t>
+          <t>basic tuff</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -6279,7 +6279,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>peralkaline syenites: pulaskite</t>
+          <t>alkaline basalt</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -6289,7 +6289,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>goyaite</t>
+          <t>slate; alluvial sediments</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -6299,7 +6299,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>meta-gabbro</t>
+          <t>colluvial</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -6309,7 +6309,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>carbonatite dikes cut Precambrian dolomite</t>
+          <t>and residual sediments</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -6319,7 +6319,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>roof pendants–calcic marble</t>
+          <t>(hornblende) granodiorite</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -6329,7 +6329,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>metamorphosed felsic volcanic rock</t>
+          <t>biotite granodiorite</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -6339,7 +6339,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>calcsilicate hornfels</t>
+          <t>biotite-(hornblende) granodiorite</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -6349,7 +6349,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>muscovite–tourmaline granite</t>
+          <t>channel sand</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -6359,7 +6359,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>weathered leucogranite</t>
+          <t>leucocratic muscovite granite</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -6369,7 +6369,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>alkaline gneiss</t>
+          <t>biotite-amphibole schist  amphibolite</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -6379,7 +6379,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>aeolian dunes and beach sand</t>
+          <t>weathered granodiorite</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -6389,7 +6389,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>iron ore; tailings</t>
+          <t>limestone and bauxite</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -6399,7 +6399,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>muscovite (sericite) quartz schist</t>
+          <t>alkalic riebeckite granite</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -6409,7 +6409,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>felsic igneous or metamorphic rock (inferred</t>
+          <t>aegirine syenite</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -6419,7 +6419,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>syenite; carbonatite</t>
+          <t>laterized granite</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -6429,7 +6429,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>alkaline pyroxenites</t>
+          <t>paleosol</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -6439,7 +6439,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>carbonatite (limestone)</t>
+          <t>metasedimentary rocks</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -6449,7 +6449,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>felsic metavolcanic rock</t>
+          <t>altered syenite</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -6459,7 +6459,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>alluvium(?)</t>
+          <t>sövite and beforsite (some metamorphosed)</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -6469,7 +6469,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>calcite carbonatite lava</t>
+          <t>alkaline igneous rocks</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -6479,7 +6479,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>silicified carbonatite</t>
+          <t>phosphatic limestone</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -6489,7 +6489,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>leptynite</t>
+          <t>peralkaline rocks</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -6499,7 +6499,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>leptite</t>
+          <t>coastal plain sands</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -6509,7 +6509,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>metasediments and metavolcanics—marble</t>
+          <t>fenitized gneiss and eudialyte-aegirine-albite rock</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -6519,7 +6519,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>decomposed carbonatite breccia</t>
+          <t>iron ore</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -6529,7 +6529,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>meta-basalt</t>
+          <t>magnetite-carbonate rock</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -6539,7 +6539,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>coastal plain sands</t>
+          <t>carbonatite dikes cut Precambrian dolomite</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -6549,7 +6549,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>tremolite-actinolite schist</t>
+          <t>silicified carbonatite</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -6559,7 +6559,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>alkalic riebeckite granite</t>
+          <t>calcite carbonatite lava</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -6569,7 +6569,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>phonolite plugs</t>
+          <t>carbonatite (limestone)</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -6579,7 +6579,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>limestone and bauxite</t>
+          <t>sandstone; limestone</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -6589,7 +6589,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>weathered granodiorite</t>
+          <t>weathered syenite</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -6599,7 +6599,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>terra rossa</t>
+          <t>beach sand and dunes</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -6609,7 +6609,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>basic-ultrabasic lamprophyre</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -6619,7 +6619,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>ultramafic rocks: pyroxene</t>
+          <t>moderately to strongly hematized nepheline syenite</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -6629,7 +6629,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>felsic schist</t>
+          <t>beforsitic carbonatite</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -6639,7 +6639,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>weathered felsic rock (inferred</t>
+          <t>magnetite carbonatite</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -6649,7 +6649,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>biotite monzonite granite</t>
+          <t>ferricrete</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -6659,7 +6659,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>alkaline granite porphyry</t>
+          <t>weathered eudialyte granite</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -6669,7 +6669,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>rhyolite flow and tuff</t>
+          <t>nepheline syenite dikes</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -6679,7 +6679,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>microfoyaite</t>
+          <t>fenitized peralkaline arfvedsonite-aegirine granite and associated agpaitic pegmatites</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -6689,7 +6689,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>arenaceous sedimentary rock</t>
+          <t>eudialyte granite</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -6699,7 +6699,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>aegirinolite</t>
+          <t>agpaitic phonolite</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -6709,7 +6709,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>carbonatized intrusions</t>
+          <t>migmatite—hornblende gneiss</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -6719,7 +6719,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>granite-gneiss</t>
+          <t>theralite</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -6729,7 +6729,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>porphyritic syenite</t>
+          <t>limestone; clay; red sandstones</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -6739,7 +6739,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>brecciated syenite</t>
+          <t>hydrothermal carbonatite</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -6749,7 +6749,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>carbonatite (sövite</t>
+          <t>laterized pyroclastic ferrocarbonatite</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -6759,7 +6759,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>ankeritic carbonatite); tinguaite dykes; fenite-breccia</t>
+          <t>volcanic ash</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -6769,7 +6769,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>augite-hornblende syenite and microsyenite</t>
+          <t>syenite; carbonatite</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -6779,7 +6779,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>fayalite-augite microsyenite</t>
+          <t>alkaline gneiss</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -6789,7 +6789,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>quartz-hornblende syenite</t>
+          <t>mafic gneiss</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -6799,7 +6799,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>alkali-feldspar granite</t>
+          <t>arenaceous sedimentary rock</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -6809,7 +6809,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>eolian sand</t>
+          <t>granite-gneiss</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -6819,7 +6819,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>potassic feldspar rock</t>
+          <t>porphyritic syenite</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -6829,7 +6829,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>potassic carbonatite</t>
+          <t>brecciated syenite</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -6839,7 +6839,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>peralkaline gneiss</t>
+          <t>carbonatite (sövite</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -6849,7 +6849,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>beforsite dikes</t>
+          <t>ankeritic carbonatite); tinguaite dykes; fenite-breccia</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -6859,7 +6859,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>volcanic breccias</t>
+          <t>augite-hornblende syenite and microsyenite</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -6869,7 +6869,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>alaskite with xenoliths of metamorphic rock</t>
+          <t>fayalite-augite microsyenite</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -6879,7 +6879,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>aegerine-syenite dikes</t>
+          <t>quartz-hornblende syenite</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -6889,7 +6889,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>metadiorite</t>
+          <t>alkali-feldspar granite</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -6899,7 +6899,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>siliceous dolomite</t>
+          <t>eolian sand</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -6909,7 +6909,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>alkaline dunite</t>
+          <t>potassic carbonatite</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -6919,7 +6919,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>carbonate rocks</t>
+          <t>peralkaline gneiss</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -6929,7 +6929,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>aegerine nepheline syenite</t>
+          <t>beforsite dikes</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -6939,7 +6939,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>gray to black shale</t>
+          <t>volcanic breccias</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -6949,7 +6949,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>dolomicrite</t>
+          <t>carbonatized intrusions</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -6959,7 +6959,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>monzonitic granite</t>
+          <t>potassic feldspar rock</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -6969,7 +6969,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>porphyry</t>
+          <t>decomposed carbonatite breccia</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -6979,7 +6979,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>aegirine granite</t>
+          <t>feldspathic breccias</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -6989,7 +6989,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>nordmarkite(?)</t>
+          <t>microfoyaite</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -6999,7 +6999,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>biotite-calcite schist</t>
+          <t>trachyphonolite</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -7009,7 +7009,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>pyroxene fenite</t>
+          <t>siderite sövite</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -7019,7 +7019,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>magnesian carbonatite</t>
+          <t>metadiorite</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -7029,7 +7029,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>carbonatite and pyroxenite breccia</t>
+          <t>agglomeritic carbonatite</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -7049,7 +7049,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>agglomeritic carbonatite</t>
+          <t>magnesian carbonatite</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -7059,7 +7059,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>brucite marble</t>
+          <t>pyroxene fenite</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -7079,7 +7079,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>nepheline-aegerine rock</t>
+          <t>iron deposits</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -7089,7 +7089,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>arfvedsonite syenite</t>
+          <t>aegirine fenite</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -7099,7 +7099,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>dolomitic phosphorite</t>
+          <t>weathered pyroxenite</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -7119,7 +7119,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>metavolcanic rocks-spilite</t>
+          <t>phonolite plugs</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -7129,7 +7129,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>keratophyre</t>
+          <t>tremolite-actinolite schist</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -7139,7 +7139,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>keratophyre volcaniclastic rock</t>
+          <t>meta-basalt</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -7149,7 +7149,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>magnetic quartzite</t>
+          <t>calcsilicate hornfels</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -7159,7 +7159,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>weathered pyroxenite</t>
+          <t>weathered leucogranite</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -7169,7 +7169,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>ferromanganous carbonate</t>
+          <t>enstatite-ferrosilite granite/granodiorite</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -7179,7 +7179,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>aegirine fenite</t>
+          <t>ultramafic rocks</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -7189,7 +7189,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>volcanic carbonatite lapilli tuff</t>
+          <t>feldspathic gneiss</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -7199,7 +7199,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>and lava</t>
+          <t>monazite-dominant metasediment</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -7209,7 +7209,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>leucitite</t>
+          <t>mafic-rich quartzite</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -7219,7 +7219,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>basic and ultrabasic rocks</t>
+          <t>feldspathic breccia</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -7229,7 +7229,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>iron deposits</t>
+          <t>mafic alkaline rocks</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -7239,7 +7239,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>aegirine alkaline granite</t>
+          <t>shonkonite</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -7249,7 +7249,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>naujaite; syenite</t>
+          <t>porphyritic potassic syenite</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -7259,7 +7259,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>arfvedsonite lujavrite</t>
+          <t>silty dolomite</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -7269,7 +7269,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>fenitized gneiss and eudialyte-aegirine-albite rock</t>
+          <t>syenitic pegmatite</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -7279,7 +7279,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>peralkaline riebeckite and aegirine granites</t>
+          <t>dolomitic siltstone</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -7289,7 +7289,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>nepheline-bearing metasyenite</t>
+          <t>peralkaline riebeckite and aegirine granites</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -7299,7 +7299,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>syenitic gneiss</t>
+          <t>monzodiorite to granodiorite</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -7309,7 +7309,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>weathered syenite</t>
+          <t>nepheline-bearing metasyenite</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -7319,7 +7319,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>beach sand and dunes</t>
+          <t>syenitic gneiss</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -7349,7 +7349,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>cryptocrystalline alkaline rock</t>
+          <t>granitic and (hornblende) gneiss</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -7359,7 +7359,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>syenitic pegmatite</t>
+          <t>fenitized limestone</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -7369,7 +7369,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>colluvial sediments</t>
+          <t>garnet diatexite</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -7379,7 +7379,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>granitic dikes and small stocks(?)</t>
+          <t>rhyolitic to rhyodacitic volcanic rocks</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -7389,7 +7389,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>aluminous argillite</t>
+          <t>alkalic microgranite</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -7399,7 +7399,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>red mudstone</t>
+          <t>leucocratic microgranite-microsyenite-albitite sill</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -7409,7 +7409,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>pegmatites in amphibole syenite</t>
+          <t>porphyritic microgranite</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -7419,7 +7419,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>basic volcanics</t>
+          <t>ultramafic and mafic rocks</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -7429,7 +7429,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>nepheline syenite gneiss</t>
+          <t>metasandstone</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -7439,7 +7439,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>monzodiorite to granodiorite</t>
+          <t>pyroclastics</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -7449,7 +7449,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>dolomitic siltstone</t>
+          <t>unconsolidated tuffaceous material</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -7459,7 +7459,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>calc-silicate rock)</t>
+          <t>alkali volcanics and granite</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -7469,7 +7469,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>silty dolomite</t>
+          <t>rhyolitic to ryodacitic tuff</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -7479,7 +7479,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>subvolcanics</t>
+          <t>dolomitized limestone</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -7489,7 +7489,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>nelsonite</t>
+          <t>pseudoleucite porphyry</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -7499,7 +7499,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>rhyolitic to rhyodacitic volcanic rocks</t>
+          <t>extrusive silicic calcite carbonatite lapilli</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -7509,7 +7509,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>sandstone; limestone</t>
+          <t>alkaline volcanics</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -7519,7 +7519,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>garnet diatexite</t>
+          <t>subvolcanics</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -7529,7 +7529,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>fenitized limestone</t>
+          <t>nelsonite</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -7539,7 +7539,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>granitic and (hornblende) gneiss</t>
+          <t>cryptocrystalline alkaline rock</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -7549,7 +7549,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>feldspathic gneiss</t>
+          <t>colluvial sediments</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -7559,7 +7559,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>monazite-dominant metasediment</t>
+          <t>aeolian dunes and beach sand</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -7569,7 +7569,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>mafic-rich quartzite</t>
+          <t>quartzofeldspathic metasediments</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -7579,7 +7579,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>feldspathic breccia</t>
+          <t>melagranite</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -7589,7 +7589,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>mafic alkaline rocks</t>
+          <t>intrusive carbonatitic and other breccias</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -7599,7 +7599,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>shonkonite</t>
+          <t>ultramafic dike</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -7609,7 +7609,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>porphyritic potassic syenite</t>
+          <t>glacial sediment</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -7619,7 +7619,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>ultramafic rocks</t>
+          <t>plutonic rocks</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -7629,7 +7629,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>metamorphic rock(marble</t>
+          <t>quartzo-feldspathic gneiss</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -7639,7 +7639,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>peralkaline felsic volcanic rock</t>
+          <t>uncompahgrite</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -7649,7 +7649,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>extrusive silicic calcite carbonatite lapilli</t>
+          <t>leached carbonatite</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -7659,7 +7659,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>quartzo-feldspathic gneiss</t>
+          <t>granitic dikes and small stocks(?)</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -7669,7 +7669,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>quartzofeldspathic metasediments</t>
+          <t>residium</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -7679,7 +7679,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>leached carbonatite</t>
+          <t>dolomitic and sideritic carbonatite</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -7689,7 +7689,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>residium</t>
+          <t>gabbroic rock</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -7699,7 +7699,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>dolomitic and sideritic carbonatite</t>
+          <t>felsic volcanic</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -7709,7 +7709,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>gabbroic rock</t>
+          <t>amphibole schist</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -7719,7 +7719,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>felsic volcanic</t>
+          <t>quartz-feldspar-biotite granite</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -7729,7 +7729,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>amphibole schist</t>
+          <t>peralkaline volcano-plutonic complex</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -7739,7 +7739,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>quartz-feldspar-biotite granite</t>
+          <t>bench gravel</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -7749,7 +7749,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>peralkaline volcano-plutonic complex</t>
+          <t>mylonite</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -7759,7 +7759,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>enstatite-ferrosilite granite/granodiorite</t>
+          <t>stream and bench sediments</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -7769,7 +7769,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>arfvedsonite gneiss</t>
+          <t>limestone with associated rhyolite porphyry</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -7779,7 +7779,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>sandstone; metasemipelites</t>
+          <t>aluminous argillite</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -7789,7 +7789,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>aplitic granite</t>
+          <t>red mudstone</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -7799,7 +7799,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>breccias</t>
+          <t>pegmatites in amphibole syenite</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -7809,7 +7809,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>anorthositic gabbro</t>
+          <t>basic volcanics</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -7819,7 +7819,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>uncompahgrite</t>
+          <t>nepheline syenite gneiss</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -7829,7 +7829,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>laterized pyroclastic ferrocarbonatite</t>
+          <t>metamorphic rock(marble</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -7839,7 +7839,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>oxidized diatreme breccia</t>
+          <t>calc-silicate rock)</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -7849,7 +7849,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>plutonic rocks</t>
+          <t>peralkaline felsic volcanic rock</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -7859,7 +7859,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>pantellerite</t>
+          <t>oxidized diatreme breccia</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -7869,7 +7869,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>gabbro(?)</t>
+          <t>pantellerite</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -7879,7 +7879,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>hematitic sandstone</t>
+          <t>gabbro(?)</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -7889,7 +7889,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>pulaskite dikes in Cretaceous granitic pluton</t>
+          <t>hematitic sandstone</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -7899,7 +7899,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>stream sediments</t>
+          <t>pulaskite dikes in Cretaceous granitic pluton</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -7909,7 +7909,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>and schist</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -7919,7 +7919,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>limestone with associated rhyolite porphyry</t>
+          <t>stream sediments</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -7929,7 +7929,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>stream and bench sediments</t>
+          <t>aplite-pegmatite</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -7939,7 +7939,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>mylonite</t>
+          <t>arfvedsonite-alkali feldspar microgranite</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -7949,7 +7949,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>bench gravel</t>
+          <t>porphyritic</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -7959,7 +7959,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>volcanic ash</t>
+          <t>garnet-cordierite-mica gneiss</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -7969,7 +7969,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>melagranite</t>
+          <t>peralkaline syenites: pulaskite</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -7979,7 +7979,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>intrusive carbonatitic and other breccias</t>
+          <t>goyaite</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -7989,7 +7989,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>ultramafic dike</t>
+          <t>naujaite; syenite</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -7999,7 +7999,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>glacial sediment</t>
+          <t>arfvedsonite lujavrite</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -8009,7 +8009,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>alkaline volcanics</t>
+          <t>iron formation(?)</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -8019,7 +8019,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>pseudoleucite porphyry</t>
+          <t>hornblendite</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -8029,7 +8029,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>peralkaline rocks</t>
+          <t>quartz-sericite rock</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -8039,7 +8039,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>phosphatic limestone</t>
+          <t>alkaline schist and gneiss</t>
         </is>
       </c>
       <c r="B762" t="n">
@@ -8049,7 +8049,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>dolomite-carbonatite</t>
+          <t>mafic pyroxene diabase</t>
         </is>
       </c>
       <c r="B763" t="n">
@@ -8059,7 +8059,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>kaolinitic saprolite</t>
+          <t>metavolcanic rocks</t>
         </is>
       </c>
       <c r="B764" t="n">
@@ -8069,7 +8069,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>massive magnetite rock</t>
+          <t>fayalite ferrogabbro</t>
         </is>
       </c>
       <c r="B765" t="n">
@@ -8079,7 +8079,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>sericite quartzite</t>
+          <t>fayalite</t>
         </is>
       </c>
       <c r="B766" t="n">
@@ -8089,7 +8089,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>arkosic sandstone</t>
+          <t>ferrogabbro</t>
         </is>
       </c>
       <c r="B767" t="n">
@@ -8099,7 +8099,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>alkaline igneous rocks</t>
+          <t>jacupirangite dike</t>
         </is>
       </c>
       <c r="B768" t="n">
@@ -8109,7 +8109,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>pyroxene tonalite</t>
+          <t>mica gneiss</t>
         </is>
       </c>
       <c r="B769" t="n">
@@ -8119,7 +8119,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>alkaline intrusive</t>
+          <t>calc-silicate gneiss</t>
         </is>
       </c>
       <c r="B770" t="n">
@@ -8129,7 +8129,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>tuffisite</t>
+          <t>metavolcanic rock(?)</t>
         </is>
       </c>
       <c r="B771" t="n">
@@ -8139,7 +8139,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>ultrabasic rock</t>
+          <t>carbonate-sericite-schist</t>
         </is>
       </c>
       <c r="B772" t="n">
@@ -8149,7 +8149,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>grännerite</t>
+          <t>metatrachydacite</t>
         </is>
       </c>
       <c r="B773" t="n">
@@ -8159,7 +8159,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>reef limestone</t>
+          <t>sandy siltstone</t>
         </is>
       </c>
       <c r="B774" t="n">
@@ -8169,7 +8169,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>sedimentary quartz-feldspar gneiss</t>
+          <t>iron ore; tailings</t>
         </is>
       </c>
       <c r="B775" t="n">
@@ -8179,7 +8179,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>alkaline gneissic granite</t>
+          <t>muscovite (sericite) quartz schist</t>
         </is>
       </c>
       <c r="B776" t="n">
@@ -8189,7 +8189,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>albite-carbonate rock</t>
+          <t>alkaline pyroxenites</t>
         </is>
       </c>
       <c r="B777" t="n">
@@ -8199,7 +8199,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>calcite-carbonatite</t>
+          <t>felsic metavolcanic rock</t>
         </is>
       </c>
       <c r="B778" t="n">
@@ -8209,7 +8209,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>kakortokite (agpaitic nepheline syenite)</t>
+          <t>alluvium(?)</t>
         </is>
       </c>
       <c r="B779" t="n">
@@ -8219,7 +8219,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>alkaline granite(?)</t>
+          <t>metamorphosed felsic volcanic rock</t>
         </is>
       </c>
       <c r="B780" t="n">
@@ -8229,7 +8229,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>graphitic gneiss</t>
+          <t>topaz-bearing granite</t>
         </is>
       </c>
       <c r="B781" t="n">
@@ -8239,7 +8239,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>iron formation(?)</t>
+          <t>meta-gabbro</t>
         </is>
       </c>
       <c r="B782" t="n">
@@ -8249,7 +8249,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>hornblendite</t>
+          <t>meta-norite</t>
         </is>
       </c>
       <c r="B783" t="n">
@@ -8259,7 +8259,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>quartz-sericite rock</t>
+          <t>hematite carbonatite (rodberg)</t>
         </is>
       </c>
       <c r="B784" t="n">
@@ -8269,7 +8269,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>aegirine syenite</t>
+          <t>felsic metavolcanic rocks</t>
         </is>
       </c>
       <c r="B785" t="n">
@@ -8279,7 +8279,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>garnet-cordierite-mica gneiss</t>
+          <t>albite gneiss</t>
         </is>
       </c>
       <c r="B786" t="n">
@@ -8289,7 +8289,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>alkaline schist and gneiss</t>
+          <t>aegirine-riebeckite gneiss</t>
         </is>
       </c>
       <c r="B787" t="n">
@@ -8299,7 +8299,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>metavolcanic rocks</t>
+          <t>mangerite</t>
         </is>
       </c>
       <c r="B788" t="n">
@@ -8309,7 +8309,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>fayalite ferrogabbro</t>
+          <t>siderite carbonatite</t>
         </is>
       </c>
       <c r="B789" t="n">
@@ -8319,7 +8319,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>fayalite</t>
+          <t>monzosyenite</t>
         </is>
       </c>
       <c r="B790" t="n">
@@ -8329,7 +8329,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>ferrogabbro</t>
+          <t>olivine-magnetite rock</t>
         </is>
       </c>
       <c r="B791" t="n">
@@ -8339,7 +8339,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>jacupirangite dike</t>
+          <t>graphitic gneiss</t>
         </is>
       </c>
       <c r="B792" t="n">
@@ -8349,7 +8349,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>mica gneiss</t>
+          <t>aphyric trachyte</t>
         </is>
       </c>
       <c r="B793" t="n">
@@ -8359,7 +8359,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>calc-silicate gneiss</t>
+          <t>diabase; dioritic dykes</t>
         </is>
       </c>
       <c r="B794" t="n">
@@ -8369,7 +8369,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>monzosyenite</t>
+          <t>alkaline intrusions</t>
         </is>
       </c>
       <c r="B795" t="n">
@@ -8379,7 +8379,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>olivine-magnetite rock</t>
+          <t>carbonatites</t>
         </is>
       </c>
       <c r="B796" t="n">
@@ -8389,7 +8389,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>altered volcanic rock</t>
+          <t>ultramafics</t>
         </is>
       </c>
       <c r="B797" t="n">
@@ -8399,7 +8399,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>sövite and beforsite (some metamorphosed)</t>
+          <t>weathered arkosic gneiss</t>
         </is>
       </c>
       <c r="B798" t="n">
@@ -8409,7 +8409,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>dolomitized limestone</t>
+          <t>weathered quartz feldspar gneiss and tonalite</t>
         </is>
       </c>
       <c r="B799" t="n">
@@ -8419,7 +8419,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>peralkaline leucosyenite (oligoclasite)</t>
+          <t>pegmatite-aplite breccia</t>
         </is>
       </c>
       <c r="B800" t="n">
@@ -8429,7 +8429,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>alkali granite and volcanics</t>
+          <t>brecciated andesite porphyry</t>
         </is>
       </c>
       <c r="B801" t="n">
@@ -8439,7 +8439,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>altered pyroxenite</t>
+          <t>albite granite</t>
         </is>
       </c>
       <c r="B802" t="n">
@@ -8449,7 +8449,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>mafic pyroxene diabase</t>
+          <t>aegirine-arfvedsonite alkali feldspar granite</t>
         </is>
       </c>
       <c r="B803" t="n">
@@ -8459,7 +8459,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>porphyritic</t>
+          <t>silica-hematite rock</t>
         </is>
       </c>
       <c r="B804" t="n">
@@ -8469,7 +8469,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>arfvedsonite-alkali feldspar microgranite</t>
+          <t>sandstone (paleobeach sand)</t>
         </is>
       </c>
       <c r="B805" t="n">
@@ -8479,7 +8479,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>aplite-pegmatite</t>
+          <t>intermediate-felsic volcanics</t>
         </is>
       </c>
       <c r="B806" t="n">
@@ -8489,7 +8489,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>alkalic microgranite</t>
+          <t>peralkaline leucosyenite (oligoclasite)</t>
         </is>
       </c>
       <c r="B807" t="n">
@@ -8499,7 +8499,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>leucocratic microgranite-microsyenite-albitite sill</t>
+          <t>altered pyroxenite</t>
         </is>
       </c>
       <c r="B808" t="n">
@@ -8509,7 +8509,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>porphyritic microgranite</t>
+          <t>latite</t>
         </is>
       </c>
       <c r="B809" t="n">
@@ -8519,7 +8519,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>ultramafic and mafic rocks</t>
+          <t>alkaline granite(?)</t>
         </is>
       </c>
       <c r="B810" t="n">
@@ -8529,7 +8529,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>metasandstone</t>
+          <t>kakortokite (agpaitic nepheline syenite)</t>
         </is>
       </c>
       <c r="B811" t="n">
@@ -8539,7 +8539,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>pyroclastics</t>
+          <t>altered volcanic rock</t>
         </is>
       </c>
       <c r="B812" t="n">
@@ -8549,7 +8549,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>unconsolidated tuffaceous material</t>
+          <t>calcite-carbonatite</t>
         </is>
       </c>
       <c r="B813" t="n">
@@ -8559,7 +8559,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>alkali volcanics and granite</t>
+          <t>dolomite-carbonatite</t>
         </is>
       </c>
       <c r="B814" t="n">
@@ -8569,7 +8569,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>rhyolitic to ryodacitic tuff</t>
+          <t>kaolinitic saprolite</t>
         </is>
       </c>
       <c r="B815" t="n">
@@ -8579,7 +8579,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>laterized granite</t>
+          <t>massive magnetite rock</t>
         </is>
       </c>
       <c r="B816" t="n">
@@ -8589,7 +8589,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>intermediate-felsic volcanics</t>
+          <t>sericite quartzite</t>
         </is>
       </c>
       <c r="B817" t="n">
@@ -8599,7 +8599,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>altered syenite</t>
+          <t>arkosic sandstone</t>
         </is>
       </c>
       <c r="B818" t="n">
@@ -8609,7 +8609,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>sandstone (paleobeach sand)</t>
+          <t>pyroxene tonalite</t>
         </is>
       </c>
       <c r="B819" t="n">
@@ -8619,7 +8619,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>metasedimentary rocks</t>
+          <t>alkaline intrusive</t>
         </is>
       </c>
       <c r="B820" t="n">
@@ -8629,7 +8629,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>aphyric trachyte</t>
+          <t>tuffisite</t>
         </is>
       </c>
       <c r="B821" t="n">
@@ -8639,7 +8639,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>latite</t>
+          <t>ultrabasic rock</t>
         </is>
       </c>
       <c r="B822" t="n">
@@ -8649,7 +8649,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>diabase; dioritic dykes</t>
+          <t>grännerite</t>
         </is>
       </c>
       <c r="B823" t="n">
@@ -8659,7 +8659,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>alkaline intrusions</t>
+          <t>reef limestone</t>
         </is>
       </c>
       <c r="B824" t="n">
@@ -8669,7 +8669,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>carbonatites</t>
+          <t>sedimentary quartz-feldspar gneiss</t>
         </is>
       </c>
       <c r="B825" t="n">
@@ -8679,7 +8679,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>ultramafics</t>
+          <t>alkaline gneissic granite</t>
         </is>
       </c>
       <c r="B826" t="n">
@@ -8689,7 +8689,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>weathered arkosic gneiss</t>
+          <t>albite-carbonate rock</t>
         </is>
       </c>
       <c r="B827" t="n">
@@ -8699,80 +8699,10 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>weathered quartz feldspar gneiss and tonalite</t>
+          <t>apatite carbonatite; nepheline syenite</t>
         </is>
       </c>
       <c r="B828" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" t="inlineStr">
-        <is>
-          <t>pegmatite-aplite breccia</t>
-        </is>
-      </c>
-      <c r="B829" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="inlineStr">
-        <is>
-          <t>brecciated andesite porphyry</t>
-        </is>
-      </c>
-      <c r="B830" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" t="inlineStr">
-        <is>
-          <t>albite granite</t>
-        </is>
-      </c>
-      <c r="B831" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" t="inlineStr">
-        <is>
-          <t>aegirine-arfvedsonite alkali feldspar granite</t>
-        </is>
-      </c>
-      <c r="B832" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" t="inlineStr">
-        <is>
-          <t>silica-hematite rock</t>
-        </is>
-      </c>
-      <c r="B833" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" t="inlineStr">
-        <is>
-          <t>paleosol</t>
-        </is>
-      </c>
-      <c r="B834" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" t="inlineStr">
-        <is>
-          <t>apatite carbonatite; nepheline syenite</t>
-        </is>
-      </c>
-      <c r="B835" t="n">
         <v>1</v>
       </c>
     </row>
